--- a/data/analysis_pixtral_12b_qwen2_audio/multimodal_event_eval_pixtral_12b_qwen2_audio_w2_5s_h1_25s.xlsx
+++ b/data/analysis_pixtral_12b_qwen2_audio/multimodal_event_eval_pixtral_12b_qwen2_audio_w2_5s_h1_25s.xlsx
@@ -103,10 +103,10 @@
     <t>YES</t>
   </si>
   <si>
-    <t>fight(24-144)</t>
-  </si>
-  <si>
-    <t>fight(48-168)</t>
+    <t>sound: shout(0-240), visual: physical_altercation(24-144), visual: physical_altercation(144-144), visual: running(144-144), visual: running(72-144), visual: running(144-144)</t>
+  </si>
+  <si>
+    <t>sound: shout(0-240), visual: physical_altercation(48-96), visual: physical_altercation(144-168), visual: physical_altercation(120-120), visual: physical_altercation(144-168), visual: running(72-72), visual: suspicious_near_vehicle(0-48), visual: suspicious_near_vehicle(0-48), visual: suspicious_near_vehicle(72-120), visual: suspicious_near_vehicle(120-120)</t>
   </si>
   <si>
     <t>NO</t>
@@ -115,49 +115,43 @@
     <t>sound: shout(0-240), sound: impact(120-180), visual: carrying(216-216), visual: carrying(168-168), visual: carrying(192-192), visual: carrying(120-120)</t>
   </si>
   <si>
-    <t>gunshot_or_explosion(60-240)</t>
-  </si>
-  <si>
     <t>sound: engine(0-60), sound: engine(180-240), sound: impact(30-210), sound: gunshot_or_explosion(60-150), visual: carrying(168-192), visual: explosion_visible(144-240), visual: explosion_visible(168-168), visual: explosion_visible(192-240), visual: explosion_visible(120-120), visual: explosion_visible(144-240), visual: running(120-144), visual: running(144-240), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(0-24), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(120-120), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(96-96), visual: vehicle_collision(120-240)</t>
   </si>
   <si>
-    <t>gunshot_or_explosion(30-90)</t>
-  </si>
-  <si>
-    <t>gunshot_or_explosion(90-240)</t>
-  </si>
-  <si>
-    <t>gunshot_or_explosion(0-240)</t>
+    <t>sound: engine(0-60), sound: gunshot_or_explosion(30-90), sound: impact(60-120), sound: shout(90-240), visual: enter_or_exit_vehicle(72-72), visual: enter_or_exit_vehicle(120-120), visual: enter_or_exit_vehicle(0-0), visual: suspicious_near_vehicle(72-120), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(72-72)</t>
+  </si>
+  <si>
+    <t>sound: shout(0-240), sound: gunshot_or_explosion(90-150), sound: impact(120-180), visual: enter_or_exit_vehicle(48-48), visual: enter_or_exit_vehicle(96-96), visual: explosion_visible(120-240), visual: gunshot_visible(120-240), visual: running(120-240), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-216), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(240-240), visual: suspicious_near_vehicle(144-216)</t>
+  </si>
+  <si>
+    <t>sound: gunshot_or_explosion(0-60), sound: engine(30-90), sound: engine(150-240), sound: shout(60-180), visual: explosion_visible(120-120), visual: explosion_visible(120-120), visual: explosion_visible(48-48), visual: explosion_visible(168-168), visual: explosion_visible(24-240), visual: explosion_visible(120-240), visual: explosion_visible(192-240), visual: running(48-240), visual: running(120-240), visual: running(120-240)</t>
   </si>
   <si>
     <t>sound: gunshot_or_explosion(0-90), sound: shout(60-240), visual: enter_or_exit_vehicle(0-24), visual: explosion_visible(48-240), visual: explosion_visible(144-240), visual: explosion_visible(48-72), visual: explosion_visible(144-240), visual: explosion_visible(216-240), visual: running(144-240), visual: suspicious_near_vehicle(0-24), visual: vehicle_collision(0-240)</t>
   </si>
   <si>
-    <t>vehicle_escape(30-210)</t>
-  </si>
-  <si>
-    <t>vehicle_escape(60-240)</t>
+    <t>sound: shout(0-60), sound: shout(180-240), sound: engine(30-150), sound: tire_squeal(120-210), visual: enter_or_exit_vehicle(48-48), visual: suspicious_near_vehicle(48-48), visual: suspicious_near_vehicle(168-168)</t>
+  </si>
+  <si>
+    <t>sound: tire_squeal(0-60), sound: tire_squeal(150-240), sound: shout(30-90), sound: engine(60-180)</t>
   </si>
   <si>
     <t>sound: shout(0-90), sound: engine(60-210), sound: tire_squeal(180-240), visual: enter_or_exit_vehicle(48-48), visual: suspicious_near_vehicle(0-48), visual: suspicious_near_vehicle(168-168), visual: vehicle_collision(168-168)</t>
   </si>
   <si>
-    <t>vehicle_collision(0-150)</t>
-  </si>
-  <si>
-    <t>vehicle_collision(72-240)</t>
-  </si>
-  <si>
-    <t>vehicle_collision(0-240)</t>
+    <t>sound: horn(0-90), sound: horn(150-210), sound: glass_breaking(60-150), sound: shout(120-240), visual: carrying(48-48), visual: enter_or_exit_vehicle(192-192), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(96-96)</t>
+  </si>
+  <si>
+    <t>sound: tire_squeal(0-90), sound: glass_breaking(60-150), sound: shout(120-240), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
+  </si>
+  <si>
+    <t>sound: horn(0-60), sound: shout(30-90), sound: shout(180-240), sound: impact(60-120), sound: glass_breaking(90-150), sound: engine(120-210), visual: enter_or_exit_vehicle(120-216), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-216), visual: suspicious_near_vehicle(168-240), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(120-240), visual: vehicle_collision(192-240)</t>
   </si>
   <si>
     <t>visual: enter_or_exit_vehicle(24-48), visual: enter_or_exit_vehicle(192-216), visual: suspicious_near_vehicle(24-144), visual: suspicious_near_vehicle(168-216)</t>
   </si>
   <si>
-    <t>loitering(24-216)</t>
-  </si>
-  <si>
-    <t>loitering(0-240)</t>
+    <t>visual: carrying(24-48), visual: suspicious_near_vehicle(24-216)</t>
   </si>
   <si>
     <t>visual: carrying(144-192), visual: enter_or_exit_vehicle(96-192), visual: running(72-120), visual: suspicious_near_vehicle(0-240)</t>
@@ -166,34 +160,40 @@
     <t>visual: carrying(24-48), visual: carrying(0-0), visual: carrying(144-240), visual: carrying(72-120), visual: carrying(168-240), visual: carrying(72-144)</t>
   </si>
   <si>
-    <t>handoff(120-216), handoff(0-120), handoff(0-120), handoff(0-168), handoff(120-216), handoff(0-120), handoff(0-120), handoff(0-168)</t>
-  </si>
-  <si>
-    <t>handoff(0-24), handoff(24-192), handoff(0-24), handoff(24-192)</t>
+    <t>visual: carrying(96-96), visual: carrying(240-240), visual: carrying(144-216), visual: carrying(0-120), visual: carrying(120-120), visual: carrying(144-144), visual: carrying(24-24), visual: carrying(96-96), visual: carrying(168-168), visual: carrying(192-240), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(240-240), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(216-216)</t>
+  </si>
+  <si>
+    <t>visual: carrying(0-0), visual: carrying(120-192), visual: carrying(48-96), visual: carrying(72-72), visual: carrying(24-24), visual: carrying(144-192), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(48-48)</t>
   </si>
   <si>
     <t>sound: shout(0-240), visual: physical_altercation(48-120), visual: physical_altercation(144-168)</t>
   </si>
   <si>
-    <t>fight(48-120)</t>
-  </si>
-  <si>
-    <t>vehicle_escape(24-210)</t>
-  </si>
-  <si>
-    <t>vehicle_escape(0-180)</t>
+    <t>sound: shout(0-240), visual: physical_altercation(48-120), visual: running(24-120), visual: running(192-192), visual: running(24-120), visual: running(192-192)</t>
+  </si>
+  <si>
+    <t>sound: shout(0-150), sound: impact(60-120), sound: tire_squeal(120-210), sound: engine(180-240), visual: carrying(48-72), visual: carrying(0-24), visual: carrying(120-144), visual: enter_or_exit_vehicle(72-72), visual: running(24-24), visual: suspicious_near_vehicle(0-48)</t>
   </si>
   <si>
     <t>sound: shout(0-120), sound: engine(90-240), sound: tire_squeal(120-180), visual: enter_or_exit_vehicle(48-168), visual: running(0-0), visual: suspicious_near_vehicle(0-168)</t>
   </si>
   <si>
-    <t>loitering(0-216)</t>
-  </si>
-  <si>
-    <t>loitering(24-240)</t>
-  </si>
-  <si>
-    <t>handoff(0-48), handoff(0-168), handoff(24-240), handoff(120-240), handoff(0-48), handoff(24-240), handoff(0-168), handoff(120-240)</t>
+    <t>visual: enter_or_exit_vehicle(48-168), visual: running(0-0), visual: suspicious_near_vehicle(0-168)</t>
+  </si>
+  <si>
+    <t>sound: horn(0-90), sound: glass_breaking(60-120), sound: shout(90-240), sound: engine(120-180), visual: 9(216-216), visual: 9(216-216), visual: enter_or_exit_vehicle(168-216), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(72-240), visual: vehicle_collision(144-144), visual: vehicle_collision(96-120), visual: vehicle_collision(192-240), visual: vehicle_collision(72-72), visual: vehicle_collision(168-168)</t>
+  </si>
+  <si>
+    <t>sound: tire_squeal(0-60), sound: impact(30-90), sound: impact(180-240), sound: glass_breaking(60-120), sound: shout(90-180), sound: engine(150-210), visual: enter_or_exit_vehicle(168-168), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(72-120), visual: vehicle_collision(72-240)</t>
+  </si>
+  <si>
+    <t>visual: carrying(0-24), visual: carrying(48-192), visual: enter_or_exit_vehicle(72-144), visual: running(216-216), visual: suspicious_near_vehicle(0-216)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(48-144), visual: running(192-216), visual: suspicious_near_vehicle(24-240)</t>
+  </si>
+  <si>
+    <t>visual: carrying(0-0), visual: carrying(144-240), visual: carrying(72-96), visual: carrying(24-48), visual: carrying(120-168)</t>
   </si>
   <si>
     <t>visual: carrying(192-240), visual: carrying(24-168), visual: carrying(144-144), visual: walking(192-192)</t>
@@ -780,51 +780,51 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -885,6 +885,50 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>31</v>
       </c>
     </row>
@@ -893,31 +937,31 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>15</v>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -937,31 +981,31 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>16</v>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>17</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
@@ -981,40 +1025,40 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>17</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>34</v>
@@ -1025,40 +1069,40 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>18</v>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>19</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
       </c>
       <c r="E2" t="s">
         <v>35</v>
@@ -1069,31 +1113,31 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>19</v>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>20</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
@@ -1106,50 +1150,6 @@
       </c>
       <c r="E2" t="s">
         <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1166,6 +1166,138 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1174,75 +1306,119 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
       <c r="D2" t="s">
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>4</v>
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>30</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -1254,94 +1430,6 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1350,40 +1438,40 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
       </c>
       <c r="E2" t="s">
         <v>42</v>
@@ -1394,34 +1482,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -1431,94 +1519,6 @@
       </c>
       <c r="E2" t="s">
         <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>32</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1535,95 +1535,95 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1948,6 +1948,50 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1956,35 +2000,35 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>9</v>
       </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
       <c r="C2" t="s">
         <v>18</v>
       </c>
@@ -2000,35 +2044,35 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
       <c r="C2" t="s">
         <v>18</v>
       </c>
@@ -2037,50 +2081,6 @@
       </c>
       <c r="E2" t="s">
         <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2141,7 +2141,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_pixtral_12b_qwen2_audio/multimodal_event_eval_pixtral_12b_qwen2_audio_w2_5s_h1_25s.xlsx
+++ b/data/analysis_pixtral_12b_qwen2_audio/multimodal_event_eval_pixtral_12b_qwen2_audio_w2_5s_h1_25s.xlsx
@@ -718,22 +718,22 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0.833</v>
+        <v>0.8</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="D7">
-        <v>0.909</v>
+        <v>0.8</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -1468,10 +1468,10 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>42</v>

--- a/data/analysis_pixtral_12b_qwen2_audio/multimodal_event_eval_pixtral_12b_qwen2_audio_w2_5s_h1_25s.xlsx
+++ b/data/analysis_pixtral_12b_qwen2_audio/multimodal_event_eval_pixtral_12b_qwen2_audio_w2_5s_h1_25s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="52">
   <si>
     <t>event</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>sound: tire_squeal(0-90), sound: glass_breaking(60-150), sound: shout(120-240), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
   </si>
   <si>
     <t>sound: horn(0-60), sound: shout(30-90), sound: shout(180-240), sound: impact(60-120), sound: glass_breaking(90-150), sound: engine(120-210), visual: enter_or_exit_vehicle(120-216), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-216), visual: suspicious_near_vehicle(168-240), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(120-240), visual: vehicle_collision(192-240)</t>
@@ -666,22 +669,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="C5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -939,7 +942,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -976,6 +979,23 @@
         <v>32</v>
       </c>
     </row>
+    <row r="3" spans="1:5">
+      <c r="A3">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1017,7 +1037,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1055,13 +1075,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1105,7 +1125,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1149,7 +1169,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1166,7 +1186,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1210,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1298,7 +1318,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1342,7 +1362,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1386,7 +1406,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1430,7 +1450,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1474,7 +1494,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1518,7 +1538,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1535,7 +1555,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1579,7 +1599,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1623,7 +1643,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1667,7 +1687,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1711,7 +1731,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1799,7 +1819,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1843,7 +1863,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
